--- a/AtchisonRegime/Outputs/Aust/ASX300_Materials/df_regTrendSummaryASX300_Materials.xlsx
+++ b/AtchisonRegime/Outputs/Aust/ASX300_Materials/df_regTrendSummaryASX300_Materials.xlsx
@@ -1462,13 +1462,13 @@
         <v>45351</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="E47" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.08626110315509194</v>
+        <v>-0.08747091785826677</v>
       </c>
     </row>
   </sheetData>
